--- a/modules/materials_whamcavity.xlsx
+++ b/modules/materials_whamcavity.xlsx
@@ -56,13 +56,13 @@
     <t>シージング</t>
   </si>
   <si>
-    <t>-math.log(1 - r)/0.1612944</t>
-  </si>
-  <si>
-    <t>2.446*r*100-209.9</t>
-  </si>
-  <si>
-    <t>639.22-14.988*r*100+ 0.08943*r*r*10000</t>
+    <t>-math.log(1 - r)/0.1612944/100</t>
+  </si>
+  <si>
+    <t>(2.446*r*100-209.9)/100</t>
+  </si>
+  <si>
+    <t>(639.22-14.988*r*100+ 0.08943*r*r*10000)/100</t>
   </si>
   <si>
     <t>通気層</t>
@@ -662,16 +662,16 @@
         <v>13</v>
       </c>
       <c r="I2" s="2">
+        <v>0.89</v>
+      </c>
+      <c r="J2" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="K2" s="2">
         <v>0.95</v>
       </c>
-      <c r="J2" s="1" t="s">
+      <c r="L2" s="9" t="s">
         <v>14</v>
-      </c>
-      <c r="K2" s="2">
-        <v>0.89</v>
-      </c>
-      <c r="L2" s="9" t="s">
-        <v>15</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="20.25">

--- a/modules/materials_whamcavity.xlsx
+++ b/modules/materials_whamcavity.xlsx
@@ -724,7 +724,7 @@
         <v>1.19</v>
       </c>
       <c r="G4" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H4" s="1" t="s">
         <v>19</v>
@@ -1028,7 +1028,7 @@
         <v>1.154</v>
       </c>
       <c r="G14" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H14" s="1" t="s">
         <v>19</v>
@@ -1062,7 +1062,7 @@
         <v>1.164</v>
       </c>
       <c r="G15" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H15" s="1" t="s">
         <v>19</v>
@@ -1096,7 +1096,7 @@
         <v>1.152</v>
       </c>
       <c r="G16" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H16" s="1" t="s">
         <v>19</v>
@@ -1130,7 +1130,7 @@
         <v>1.162</v>
       </c>
       <c r="G17" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H17" s="1" t="s">
         <v>19</v>
@@ -1164,7 +1164,7 @@
         <v>1.181</v>
       </c>
       <c r="G18" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H18" s="1" t="s">
         <v>19</v>
